--- a/site/StructureDefinition-hcen-procedimiento.xlsx
+++ b/site/StructureDefinition-hcen-procedimiento.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3141" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3141" uniqueCount="516">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T01:23:13-03:00</t>
+    <t>2026-10-28T18:02:56-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -886,7 +886,7 @@
 </t>
   </si>
   <si>
-    <t>Código que identifica el procedimiento (SNOMED CT u otra terminología)</t>
+    <t>Código que identifica el procedimiento (SNOMED CT u otra terminología, p.ej. un tesauro clínico institucional)</t>
   </si>
   <si>
     <t>0..1 to account for primarily narrative only resources.</t>
@@ -926,6 +926,12 @@
     <t>Procedure.code.coding</t>
   </si>
   <si>
+    <t>Slicing abierto por system: además del slice snomed, admite otra codificación con su propio system — p.ej. un código de un tesauro clínico (ver sección 4.7.4 Tesauro clínico)</t>
+  </si>
+  <si>
+    <t>El slicing es abierto por system. Además del slice snomed, se puede incluir una codificación adicional de otro vocabulario — p.ej. un código de un tesauro clínico (ver [Tesauro clínico](hcen-terminologia.html#tesauro-clínico), sección 4.7.4). La URI de ese system depende de la institución de origen y su confirmación es externa a esta guía; no se fija ni se valida en este perfil.</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:system}
 </t>
   </si>
@@ -1333,7 +1339,7 @@
     <t>Procedure.outcome</t>
   </si>
   <si>
-    <t>Resultado del procedimiento (SNOMED CT u otra terminología)</t>
+    <t>Resultado del procedimiento (SNOMED CT u otra terminología, p.ej. un tesauro clínico institucional)</t>
   </si>
   <si>
     <t>If outcome contains narrative text only, it can be captured using the CodeableConcept.text.</t>
@@ -5741,10 +5747,10 @@
         <v>219</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>220</v>
+        <v>293</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>221</v>
+        <v>294</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>222</v>
@@ -5787,7 +5793,7 @@
         <v>20</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -5829,13 +5835,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>292</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>20</v>
@@ -5860,10 +5866,10 @@
         <v>219</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>222</v>
@@ -5950,10 +5956,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6065,10 +6071,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6182,10 +6188,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6284,7 +6290,7 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
@@ -6301,10 +6307,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6418,10 +6424,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6483,7 +6489,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6516,7 +6522,7 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>
@@ -6533,10 +6539,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6562,10 +6568,10 @@
         <v>207</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
@@ -6633,7 +6639,7 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
@@ -6650,10 +6656,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6769,10 +6775,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6888,14 +6894,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6914,13 +6920,13 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6971,7 +6977,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>87</v>
@@ -6986,27 +6992,27 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7029,16 +7035,16 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7088,7 +7094,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7106,24 +7112,24 @@
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7146,16 +7152,16 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7205,7 +7211,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7223,24 +7229,24 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7263,13 +7269,13 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7320,7 +7326,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7341,10 +7347,10 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7352,10 +7358,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7378,13 +7384,13 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7435,7 +7441,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7456,10 +7462,10 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7467,10 +7473,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7493,13 +7499,13 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7550,7 +7556,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7568,10 +7574,10 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>20</v>
@@ -7582,10 +7588,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7697,10 +7703,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7814,14 +7820,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7843,16 +7849,16 @@
         <v>133</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>136</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7901,7 +7907,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7933,10 +7939,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7962,14 +7968,14 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7997,10 +8003,10 @@
         <v>195</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -8018,7 +8024,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8036,24 +8042,24 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8076,17 +8082,17 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8135,7 +8141,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>87</v>
@@ -8153,24 +8159,24 @@
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8193,17 +8199,17 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8252,7 +8258,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8273,7 +8279,7 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>20</v>
@@ -8284,10 +8290,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8310,17 +8316,17 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8369,7 +8375,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8390,10 +8396,10 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -8401,10 +8407,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8430,13 +8436,13 @@
         <v>191</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8465,10 +8471,10 @@
         <v>195</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
@@ -8486,7 +8492,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8504,13 +8510,13 @@
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -8518,10 +8524,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8544,16 +8550,16 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8603,7 +8609,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8621,13 +8627,13 @@
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>20</v>
@@ -8635,10 +8641,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8664,13 +8670,13 @@
         <v>191</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8699,10 +8705,10 @@
         <v>195</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -8720,7 +8726,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8741,21 +8747,21 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8781,13 +8787,13 @@
         <v>191</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8816,10 +8822,10 @@
         <v>195</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -8837,7 +8843,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8852,13 +8858,13 @@
         <v>284</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>20</v>
@@ -8869,10 +8875,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8984,10 +8990,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9101,10 +9107,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9130,10 +9136,10 @@
         <v>219</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>220</v>
+        <v>293</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>221</v>
+        <v>294</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>222</v>
@@ -9176,7 +9182,7 @@
         <v>20</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
@@ -9218,13 +9224,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>20</v>
@@ -9249,10 +9255,10 @@
         <v>219</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>222</v>
@@ -9322,7 +9328,7 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>20</v>
@@ -9339,10 +9345,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9454,10 +9460,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9571,10 +9577,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9690,10 +9696,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9807,10 +9813,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9872,7 +9878,7 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>20</v>
@@ -9922,10 +9928,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9951,10 +9957,10 @@
         <v>207</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
@@ -10039,10 +10045,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10158,10 +10164,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10277,10 +10283,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10303,16 +10309,16 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10362,7 +10368,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10383,7 +10389,7 @@
         <v>20</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>20</v>
@@ -10394,10 +10400,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10423,13 +10429,13 @@
         <v>191</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10458,10 +10464,10 @@
         <v>195</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>20</v>
@@ -10479,7 +10485,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10500,7 +10506,7 @@
         <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>20</v>
@@ -10511,10 +10517,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10537,17 +10543,17 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -10596,7 +10602,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10617,7 +10623,7 @@
         <v>20</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>20</v>
@@ -10628,10 +10634,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10657,10 +10663,10 @@
         <v>191</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10690,10 +10696,10 @@
         <v>195</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>20</v>
@@ -10711,7 +10717,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10732,7 +10738,7 @@
         <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>20</v>
@@ -10743,10 +10749,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10769,13 +10775,13 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10826,7 +10832,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10841,27 +10847,27 @@
         <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10884,13 +10890,13 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10941,7 +10947,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10962,7 +10968,7 @@
         <v>20</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>20</v>
@@ -10973,10 +10979,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11088,10 +11094,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11205,14 +11211,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11234,16 +11240,16 @@
         <v>133</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>136</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -11292,7 +11298,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11324,10 +11330,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11353,10 +11359,10 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11386,10 +11392,10 @@
         <v>111</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>20</v>
@@ -11407,7 +11413,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11428,7 +11434,7 @@
         <v>20</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>20</v>
@@ -11439,10 +11445,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11465,13 +11471,13 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11522,7 +11528,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>87</v>
@@ -11543,7 +11549,7 @@
         <v>20</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>20</v>
@@ -11554,10 +11560,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11580,19 +11586,19 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -11641,7 +11647,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11662,7 +11668,7 @@
         <v>20</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>20</v>
@@ -11673,10 +11679,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11702,13 +11708,13 @@
         <v>191</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11737,10 +11743,10 @@
         <v>195</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>20</v>
@@ -11758,7 +11764,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11779,7 +11785,7 @@
         <v>20</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>20</v>
